--- a/cafe_data.xlsx
+++ b/cafe_data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8580" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Товары" sheetId="1" r:id="rId1"/>
@@ -13,20 +13,7 @@
     <sheet name="Сезонная история" sheetId="4" r:id="rId4"/>
     <sheet name="Инструкция" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -41,8 +28,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Название товара</t>
         </r>
@@ -53,8 +41,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>готовый или напиток</t>
         </r>
@@ -65,8 +54,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Закупочная цена в 1 периоде, ₽</t>
         </r>
@@ -77,8 +67,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Закупочная цена во 2 периоде, ₽</t>
         </r>
@@ -89,8 +80,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Цена продажи в 1 периоде, ₽</t>
         </r>
@@ -101,8 +93,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Цена продажи во 2 периоде, ₽</t>
         </r>
@@ -113,8 +106,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано штук в 1 периоде</t>
         </r>
@@ -125,8 +119,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано штук во 2 периоде</t>
         </r>
@@ -137,8 +132,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Закуплено штук в 1 периоде</t>
         </r>
@@ -149,8 +145,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Закуплено штук во 2 периоде</t>
         </r>
@@ -161,8 +158,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Остаток на начало 1 периода, шт</t>
         </r>
@@ -173,8 +171,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Остаток на начало 2 периода, шт</t>
         </r>
@@ -195,8 +194,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Дата в формате 2026-01-01</t>
         </r>
@@ -207,8 +207,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Сколько людей зашло в кафе в этот день</t>
         </r>
@@ -219,8 +220,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Чипсы</t>
         </r>
@@ -231,8 +233,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Печенье</t>
         </r>
@@ -243,8 +246,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Шоколад</t>
         </r>
@@ -255,8 +259,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Кофе</t>
         </r>
@@ -267,8 +272,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Чай</t>
         </r>
@@ -279,8 +285,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Продано: ПРИМЕР: Вода</t>
         </r>
@@ -301,8 +308,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>зима / весна / лето / осень</t>
         </r>
@@ -313,8 +321,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Название товара (как в листе «Товары»)</t>
         </r>
@@ -325,8 +334,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Средние продажи штук в день за этот сезон</t>
         </r>
@@ -337,8 +347,9 @@
         <r>
           <rPr>
             <sz val="8"/>
+            <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Средний поток гостей в день за этот сезон</t>
         </r>
@@ -459,10 +470,10 @@
     <t>зима</t>
   </si>
   <si>
+    <t>Гостей</t>
+  </si>
+  <si>
     <t>Постоянные издержки, ₽</t>
-  </si>
-  <si>
-    <t>Гостей</t>
   </si>
   <si>
     <t>⚠ Это ПРИМЕР. Заполните реальными продажами по дням. Дату пишите в формате ГГГГ-ММ-ДД, например 2026-01-15.</t>
@@ -660,19 +671,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -680,183 +704,17 @@
       <sz val="12"/>
       <color rgb="FF305496"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
+      <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -875,194 +733,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1085,345 +757,37 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1706,299 +1070,299 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.712962962963" customWidth="1"/>
-    <col min="2" max="2" width="12.712962962963" customWidth="1"/>
-    <col min="3" max="12" width="14.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="12" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:12">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="4">
         <v>45</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="4">
         <v>55</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>90</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>110</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>3500</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>3100</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>5000</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>4500</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>800</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>2300</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>30</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="4">
         <v>38</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="4">
         <v>70</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>85</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>4300</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>3900</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>5000</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>4500</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>500</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>1200</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>60</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>75</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="4">
         <v>120</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>150</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>2400</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>2100</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>3000</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>2500</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>300</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>25</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>32</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="4">
         <v>100</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>130</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>5800</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>6300</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>7000</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>7000</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>500</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>1700</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>10</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="4">
         <v>14</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="4">
         <v>60</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="4">
         <v>80</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>7200</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>6600</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>8000</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>7500</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>400</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>1200</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>15</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <v>20</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <v>50</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <v>65</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>8500</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>6200</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>9000</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>7000</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>200</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>700</v>
       </c>
     </row>
@@ -2012,103 +1376,101 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.712962962963" customWidth="1"/>
-    <col min="2" max="3" width="22.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="3" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="4">
+        <v>500</v>
+      </c>
+      <c r="C7" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="4">
         <v>30000</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C8" s="4">
         <v>32000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="8">
-        <v>500</v>
-      </c>
-      <c r="C8" s="8">
-        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -2121,862 +1483,860 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.712962962963" customWidth="1"/>
-    <col min="2" max="2" width="10.712962962963" customWidth="1"/>
-    <col min="3" max="8" width="14.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="8" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" ht="28.8" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>394</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>95</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>136</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>71</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>176</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>221</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>449</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>99</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>156</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>77</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>164</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>207</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>667</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>167</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>194</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>95</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>292</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>280</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>709</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>179</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>176</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>122</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>296</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>290</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>380</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>104</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>146</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>74</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>179</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>223</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>423</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>100</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>124</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>76</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>168</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>249</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>457</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>110</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>121</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>78</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>196</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>219</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>390</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>112</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>159</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>83</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>218</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>250</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>404</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>98</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>121</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>85</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>176</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>241</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>669</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>159</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>186</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>111</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>279</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>336</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>660</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>176</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>184</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>107</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>255</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>344</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>389</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>104</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>153</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>71</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>172</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>263</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>414</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>108</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>139</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <v>65</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>176</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>208</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>431</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>111</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>123</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <v>70</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>198</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>244</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>443</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>119</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>160</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <v>78</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <v>171</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>237</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>411</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>110</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>156</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>77</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>199</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>255</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>668</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>161</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>194</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>125</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>232</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>261</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>659</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>193</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>172</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>121</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>297</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>263</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>428</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>123</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>152</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>72</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="5">
         <v>197</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>205</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>448</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>111</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>160</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>74</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="5">
         <v>169</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>241</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>400</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>123</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>119</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>72</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>194</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>226</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>393</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>113</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>159</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>80</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>200</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>229</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>427</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>104</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>153</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>80</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>162</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>245</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>642</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>160</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>185</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="5">
         <v>113</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>251</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>262</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>712</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>158</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>167</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>125</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>229</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>323</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>396</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>102</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>161</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>79</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>197</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>225</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>271</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>447</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>121</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>132</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>81</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>210</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>229</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>431</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>117</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>147</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>80</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>190</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>219</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>408</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>98</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>140</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>64</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>199</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>274</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>455</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>108</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>119</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>66</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="5">
         <v>207</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>211</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>648</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>155</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>217</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>115</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="5">
         <v>230</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>320</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>328</v>
       </c>
     </row>
@@ -2985,209 +2345,207 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.712962962963" customWidth="1"/>
-    <col min="2" max="2" width="22.712962962963" customWidth="1"/>
-    <col min="3" max="4" width="24.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>145</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>110</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>80</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>120</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>240</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>200</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>130</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>210</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>50</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>90</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>320</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>70</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>500</v>
       </c>
     </row>
@@ -3201,167 +2559,164 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="120.712962962963" customWidth="1"/>
+    <col min="1" max="1" width="120.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="3" ht="15.6" spans="1:1">
-      <c r="A3" s="1" t="s">
+      <c r="A2" s="7"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" ht="15.6" spans="1:1">
-      <c r="A11" s="1" t="s">
+      <c r="A10" s="7"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" ht="15.6" spans="1:1">
-      <c r="A15" s="1" t="s">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="7" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" ht="15.6" spans="1:1">
-      <c r="A23" s="1" t="s">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" ht="15.6" spans="1:1">
-      <c r="A27" s="1" t="s">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="7" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>